--- a/Delhivery_Financial_Model.xlsx
+++ b/Delhivery_Financial_Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akbar\Desktop\Delhivery Research\3. Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEFAE72-9B16-4195-8A4A-7D9FD6B3F41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348CDEF3-93F7-4E95-91B9-1FC5F1ACD6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="853" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -644,7 +644,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="214">
   <si>
     <t>DELHIVERY LIMITED</t>
   </si>
@@ -667,16 +667,7 @@
     <t>Recommendation</t>
   </si>
   <si>
-    <t>HOLD (Preliminary)</t>
-  </si>
-  <si>
     <t>Current Price</t>
-  </si>
-  <si>
-    <t>Price Target (Base Case)</t>
-  </si>
-  <si>
-    <t>TBD - Week 2</t>
   </si>
   <si>
     <t>Upside / Downside</t>
@@ -1332,6 +1323,9 @@
   </si>
   <si>
     <t>It reflects that Delhivery is a high-growth company whose value lies primarily in long-term cash flow generation beyond our 5-year explicit projection period.</t>
+  </si>
+  <si>
+    <t>Scenario-Weighted Price Target</t>
   </si>
 </sst>
 </file>
@@ -1840,13 +1834,13 @@
       <c r="B9" t="s">
         <v>6</v>
       </c>
-      <c r="C9" t="s">
-        <v>7</v>
+      <c r="C9" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2">
         <v>457.9</v>
@@ -1854,18 +1848,19 @@
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
+        <v>213</v>
+      </c>
+      <c r="C11" s="2">
+        <v>580</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <f>C11/C10-1</f>
+        <v>0.26665210744704093</v>
       </c>
     </row>
   </sheetData>
@@ -1889,25 +1884,25 @@
   <sheetData>
     <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="18" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C7" s="14">
         <f>Cover!C10</f>
@@ -1916,10 +1911,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C8" s="14">
         <f>'Income Statement'!H26/'Income Statement'!H28*10</f>
@@ -1928,10 +1923,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C9" s="14">
         <f>C7*C8/10</f>
@@ -1940,31 +1935,31 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C16" s="19">
         <v>0.2</v>
@@ -1978,10 +1973,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C17" s="19">
         <v>0.25</v>
@@ -1995,10 +1990,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C18" s="19">
         <v>0.3</v>
@@ -2012,15 +2007,15 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C21" s="19">
         <v>0.92</v>
@@ -2034,10 +2029,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C22" s="19">
         <v>0.91</v>
@@ -2051,10 +2046,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C23" s="19">
         <v>0.89500000000000002</v>
@@ -2068,15 +2063,15 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C26" s="32">
         <v>780</v>
@@ -2090,10 +2085,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C27" s="32">
         <v>750</v>
@@ -2107,10 +2102,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C28" s="32">
         <v>720</v>
@@ -2124,15 +2119,15 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C31" s="32">
         <v>160</v>
@@ -2146,10 +2141,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C32" s="32">
         <v>150</v>
@@ -2163,10 +2158,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C33" s="32">
         <v>140</v>
@@ -2180,15 +2175,15 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C36" s="32">
         <v>280</v>
@@ -2202,10 +2197,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C37" s="32">
         <v>300</v>
@@ -2219,10 +2214,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C38" s="32">
         <v>320</v>
@@ -2236,15 +2231,15 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B41" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C41" s="19">
         <v>0.15</v>
@@ -2258,10 +2253,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C42" s="19">
         <v>0.1</v>
@@ -2275,10 +2270,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B43" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C43" s="19">
         <v>0.05</v>
@@ -2292,15 +2287,15 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C48" s="32">
         <f>'Balance Sheet'!$H$6</f>
@@ -2317,10 +2312,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B50" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C50" s="32">
         <f>'Balance Sheet'!$H$10</f>
@@ -2337,10 +2332,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B52" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C52" s="19">
         <v>0.1</v>
@@ -2354,10 +2349,10 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B54" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C54" s="20">
         <f>'Balance Sheet'!$H$17</f>
@@ -2374,10 +2369,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C56" s="33">
         <f>'Balance Sheet'!$H$18</f>
@@ -2394,7 +2389,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
@@ -2402,10 +2397,10 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C59" s="19">
         <f>C16</f>
@@ -2422,10 +2417,10 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B60" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C60" s="19">
         <f t="shared" ref="C60:E60" si="1">C17</f>
@@ -2442,10 +2437,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C61" s="19">
         <f t="shared" ref="C61:E61" si="2">C18</f>
@@ -2462,15 +2457,15 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B66" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C66" s="19">
         <v>4.8000000000000001E-2</v>
@@ -2484,15 +2479,15 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B69" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C69" s="19">
         <v>4.4999999999999998E-2</v>
@@ -2506,10 +2501,10 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B70" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C70" s="19">
         <v>0.04</v>
@@ -2523,10 +2518,10 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B71" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C71" s="19">
         <v>3.5000000000000003E-2</v>
@@ -2540,10 +2535,10 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B73" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C73" s="19">
         <v>2.5000000000000001E-3</v>
@@ -2577,47 +2572,47 @@
   <sheetData>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="I3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="J3" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="K3" t="s">
         <v>28</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C6" s="24">
         <v>3647</v>
@@ -2652,10 +2647,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11">
@@ -2693,10 +2688,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C8" s="24">
         <v>150</v>
@@ -2731,10 +2726,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C9" s="16">
         <f>C6+C8</f>
@@ -2775,15 +2770,15 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C12" s="24">
         <v>3769</v>
@@ -2818,15 +2813,15 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C15" s="10">
         <f t="shared" ref="C15:H15" si="8">C6-C12</f>
@@ -2867,10 +2862,10 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C16" s="11">
         <f t="shared" ref="C16:H16" si="10">C15/C6</f>
@@ -2911,10 +2906,10 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C18" s="24">
         <v>355</v>
@@ -2949,10 +2944,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C19" s="16">
         <f t="shared" ref="C19:H19" si="12">C15-C18</f>
@@ -2993,10 +2988,10 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C20" s="11">
         <f t="shared" ref="C20:H20" si="14">C19/C6</f>
@@ -3037,10 +3032,10 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C22" s="24">
         <v>89</v>
@@ -3075,10 +3070,10 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C23" s="16">
         <f t="shared" ref="C23:H23" si="16">C19-C22+C8</f>
@@ -3119,10 +3114,10 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C24" s="15">
         <v>0</v>
@@ -3157,10 +3152,10 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C25" s="26">
         <f>ABS(C23)*C24</f>
@@ -3201,10 +3196,10 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C26" s="16">
         <f>C23-C25</f>
@@ -3245,10 +3240,10 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C27" s="11">
         <f t="shared" ref="C27:H27" si="24">C26/C6</f>
@@ -3289,10 +3284,10 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C28" s="24">
         <v>-2492.6</v>
@@ -3327,7 +3322,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
@@ -3341,7 +3336,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
@@ -3355,7 +3350,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -3369,7 +3364,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -3395,47 +3390,47 @@
   <sheetData>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="I3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="J3" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="K3" t="s">
         <v>28</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C6" s="12">
         <v>2</v>
@@ -3470,10 +3465,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C7" s="9">
         <v>2800</v>
@@ -3508,10 +3503,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C8" s="10">
         <f>C6+C7</f>
@@ -3552,10 +3547,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C10" s="9">
         <v>1152</v>
@@ -3590,10 +3585,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C11" s="12">
         <v>644</v>
@@ -3628,10 +3623,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C12" s="10">
         <f>C8+C10+C11</f>
@@ -3672,15 +3667,15 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C15" s="9">
         <v>1053</v>
@@ -3715,10 +3710,10 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="17">
@@ -3756,10 +3751,10 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C17" s="12">
         <v>77</v>
@@ -3794,10 +3789,10 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C18" s="9">
         <v>1128</v>
@@ -3832,10 +3827,10 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C19" s="9">
         <v>2340</v>
@@ -3870,10 +3865,10 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C20" s="10">
         <f>C15+C17+C18+C19</f>
@@ -3915,10 +3910,10 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C22" s="10">
         <f>C20-C12</f>
@@ -3959,15 +3954,15 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C25" s="16">
         <f t="shared" ref="C25:I25" si="12">C10/C8</f>
@@ -4008,10 +4003,10 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C26" s="12">
         <v>277</v>
@@ -4048,10 +4043,10 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C27" s="10">
         <f t="shared" ref="C27:I27" si="14">C10-C26</f>
@@ -4113,47 +4108,47 @@
   <sheetData>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="I3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="J3" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="K3" t="s">
         <v>28</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C6" s="12">
         <v>5</v>
@@ -4188,10 +4183,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C7" s="12">
         <v>338</v>
@@ -4226,10 +4221,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C8" s="12">
         <v>-147</v>
@@ -4264,10 +4259,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C10" s="7">
         <f>C6+C7+C8</f>
@@ -4308,10 +4303,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C11" s="12">
         <v>-244</v>
@@ -4346,10 +4341,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C12" s="15">
         <v>-0.19</v>
@@ -4384,15 +4379,15 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C15" s="12">
         <v>251</v>
@@ -4427,10 +4422,10 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C16" s="11">
         <f>C15/'Income Statement'!C6</f>
@@ -4471,10 +4466,10 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C17" s="12">
         <v>-40</v>
@@ -4509,10 +4504,10 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C18" s="17">
         <f>C17/'Income Statement'!C6</f>
@@ -4553,10 +4548,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C19" s="11">
         <f>C11/'Income Statement'!C6</f>
@@ -4620,39 +4615,39 @@
   <sheetData>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B3" s="6"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B6">
         <v>152</v>
@@ -4678,7 +4673,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B7">
         <v>161</v>
@@ -4704,7 +4699,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B8">
         <v>170</v>
@@ -4730,7 +4725,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B9">
         <v>180</v>
@@ -4756,7 +4751,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B10">
         <v>182</v>
@@ -4782,7 +4777,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B11">
         <v>181</v>
@@ -4808,7 +4803,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B12">
         <v>201</v>
@@ -4834,7 +4829,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B13">
         <v>176</v>
@@ -4860,7 +4855,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B14">
         <v>183</v>
@@ -4886,7 +4881,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B15">
         <v>185</v>
@@ -4912,7 +4907,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B16">
         <v>206</v>
@@ -4938,7 +4933,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B17">
         <v>177</v>
@@ -4964,7 +4959,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B18">
         <v>208</v>
@@ -4990,7 +4985,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B19">
         <v>246</v>
@@ -5016,7 +5011,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B20">
         <v>295</v>
@@ -5042,7 +5037,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B21">
         <v>306</v>
@@ -5068,7 +5063,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B22">
         <v>322</v>
@@ -5115,35 +5110,35 @@
   <sheetData>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C6" s="34">
         <v>6141</v>
@@ -5164,10 +5159,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C7" s="34">
         <v>951</v>
@@ -5188,10 +5183,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C8" s="5">
         <f>C7/C6</f>
@@ -5216,10 +5211,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C9" s="34">
         <v>247</v>
@@ -5240,10 +5235,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C10" s="34">
         <v>104.26</v>
@@ -5264,10 +5259,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C11" s="5">
         <f>C6/5720-1</f>
@@ -5292,10 +5287,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C12" s="34">
         <v>11485</v>
@@ -5317,10 +5312,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C13" s="34">
         <v>1142</v>
@@ -5341,10 +5336,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C14" s="34">
         <v>239</v>
@@ -5365,10 +5360,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C15">
         <f>C12+C13-C14</f>
@@ -5393,10 +5388,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C16" s="14">
         <f>C12/C9</f>
@@ -5421,10 +5416,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C17" s="14">
         <f>C15/C7</f>
@@ -5450,10 +5445,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C18" s="14">
         <f>C12/(C9*(1+C11))</f>
@@ -5478,10 +5473,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C19" s="14">
         <f>C18/C11/100</f>
@@ -5506,10 +5501,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C20" s="34">
         <v>498</v>
@@ -5530,10 +5525,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C21" s="5">
         <f>C20/C12</f>
@@ -5558,10 +5553,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C22" s="5">
         <f>C20/C6</f>
@@ -5586,37 +5581,37 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -5641,20 +5636,20 @@
   <sheetData>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C6" s="37">
         <v>0.13</v>
@@ -5662,10 +5657,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C7" s="37">
         <v>0.04</v>
@@ -5673,10 +5668,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C8" s="14">
         <f>'Balance Sheet'!H27</f>
@@ -5685,10 +5680,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" t="s">
         <v>95</v>
-      </c>
-      <c r="B9" t="s">
-        <v>98</v>
       </c>
       <c r="C9" s="14">
         <f>Assumptions!C8</f>
@@ -5697,38 +5692,38 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C14" s="14">
         <f>'Scenario Summary'!C38</f>
@@ -5757,10 +5752,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C15" s="5">
         <f>C14/'Cash Flow'!H11-1</f>
@@ -5789,7 +5784,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C16" s="14">
         <f>1/(1+$C$6)</f>
@@ -5818,10 +5813,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C17" s="14">
         <f>C14*C16</f>
@@ -5850,10 +5845,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C19" s="14">
         <f>SUM(C17:G17)</f>
@@ -5862,10 +5857,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C20" s="14">
         <f>H17</f>
@@ -5874,10 +5869,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C21" s="14">
         <f>C19+C20</f>
@@ -5886,10 +5881,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="36" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C22" s="27">
         <f>'Balance Sheet'!H27</f>
@@ -5898,10 +5893,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C23" s="14">
         <f>C21-C22</f>
@@ -5910,10 +5905,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" t="s">
         <v>95</v>
-      </c>
-      <c r="B24" t="s">
-        <v>98</v>
       </c>
       <c r="C24" s="14">
         <f>Assumptions!C8</f>
@@ -5922,10 +5917,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B25" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C25" s="14">
         <f>C23/C24*10</f>
@@ -5934,10 +5929,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C26" s="14">
         <f>Assumptions!C7</f>
@@ -5946,10 +5941,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C27" s="5">
         <f>C25/C26-1</f>
@@ -5958,15 +5953,15 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C31" s="14">
         <f>'Scenario Summary'!C37</f>
@@ -5995,10 +5990,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C32" s="5">
         <f>C31/'Cash Flow'!H11-1</f>
@@ -6027,7 +6022,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C33" s="14">
         <f>1/(1+$C$6)</f>
@@ -6056,10 +6051,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C34" s="14">
         <f>C31*C33</f>
@@ -6088,10 +6083,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C36">
         <f>SUM(C34:G34)</f>
@@ -6100,10 +6095,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C37">
         <f>H34</f>
@@ -6112,10 +6107,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C38">
         <f>C36+C37</f>
@@ -6124,10 +6119,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="36" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B39" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C39" s="27">
         <f>'Balance Sheet'!H27</f>
@@ -6136,10 +6131,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B40" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C40" s="27">
         <f>C38-C39</f>
@@ -6148,10 +6143,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" t="s">
         <v>95</v>
-      </c>
-      <c r="B41" t="s">
-        <v>98</v>
       </c>
       <c r="C41" s="14">
         <f>Assumptions!C8</f>
@@ -6160,10 +6155,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B42" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C42" s="14">
         <f>C40/C41*10</f>
@@ -6172,10 +6167,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B43" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C43" s="14">
         <f>Assumptions!C7</f>
@@ -6184,10 +6179,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C44" s="5">
         <f>C42/C43-1</f>
@@ -6196,15 +6191,15 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C48" s="14">
         <f>'Scenario Summary'!C39</f>
@@ -6233,10 +6228,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B49" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C49" s="5">
         <f>C48/'Cash Flow'!H11-1</f>
@@ -6264,7 +6259,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C50" s="14">
         <f>1/(1+$C$6)</f>
@@ -6293,10 +6288,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B51" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C51">
         <f>C48*C50</f>
@@ -6325,10 +6320,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C53">
         <f>SUM(C51:G51)</f>
@@ -6337,10 +6332,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B54" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C54">
         <f>H51</f>
@@ -6349,10 +6344,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B55" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C55">
         <f>C53+C54</f>
@@ -6361,10 +6356,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="36" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B56" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C56" s="27">
         <f>'Balance Sheet'!H27</f>
@@ -6373,10 +6368,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B57" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C57" s="27">
         <f>C55-C56</f>
@@ -6385,10 +6380,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>92</v>
+      </c>
+      <c r="B58" t="s">
         <v>95</v>
-      </c>
-      <c r="B58" t="s">
-        <v>98</v>
       </c>
       <c r="C58" s="14">
         <f>Assumptions!C8</f>
@@ -6397,10 +6392,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B59" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C59" s="14">
         <f>C57/C58*10</f>
@@ -6409,10 +6404,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B60" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C60" s="14">
         <f>Assumptions!C7</f>
@@ -6421,10 +6416,10 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C61" s="5">
         <f>C59/C60-1</f>
@@ -6433,15 +6428,15 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B65" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C65" s="14">
         <f>C42</f>
@@ -6450,10 +6445,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B66" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C66" s="14">
         <f>C25</f>
@@ -6462,10 +6457,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B67" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C67" s="14">
         <f>C59</f>
@@ -6474,10 +6469,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B68" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C68" s="14">
         <f>25%*C65+50%*C66+25%*C67</f>
@@ -6486,10 +6481,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B69" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C69" s="5">
         <f>C68/Assumptions!C7-1</f>
@@ -6498,7 +6493,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B72" s="31"/>
       <c r="C72" s="31"/>
@@ -6627,15 +6622,15 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B84" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C84" s="14">
         <f>Assumptions!C7</f>
@@ -6644,10 +6639,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B85" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C85">
         <f>C84*C9/10</f>
@@ -6656,10 +6651,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B86" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C86" s="27">
         <f>C85+'Balance Sheet'!H27</f>
@@ -6668,10 +6663,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B87" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C87" s="14">
         <f>C86-C19</f>
@@ -6680,10 +6675,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B88" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C88">
         <f>C87/H16</f>
@@ -6692,10 +6687,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B89" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C89" s="5">
         <f>(C88/G14*C6-1)/(1+C88/G14)</f>
@@ -6704,47 +6699,47 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -6771,25 +6766,25 @@
   <sheetData>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C7" s="14">
         <f>Assumptions!C7</f>
@@ -6798,10 +6793,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" t="s">
         <v>95</v>
-      </c>
-      <c r="B8" t="s">
-        <v>98</v>
       </c>
       <c r="C8" s="14">
         <f>Assumptions!C8</f>
@@ -6811,10 +6806,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C9" s="14">
         <f>Assumptions!C9</f>
@@ -6824,10 +6819,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C10" s="14">
         <f>C9+'Balance Sheet'!H27</f>
@@ -6837,31 +6832,31 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C17" s="14">
         <f>'Income Statement'!$H$6*(1+Assumptions!C16)</f>
@@ -6878,10 +6873,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C18" s="14">
         <f>'Income Statement'!$H$6*(1+Assumptions!C17)</f>
@@ -6898,10 +6893,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C19" s="14">
         <f>'Income Statement'!$H$6*(1+Assumptions!C18)</f>
@@ -6918,15 +6913,15 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C22" s="5">
         <f>1-Assumptions!C21</f>
@@ -6943,10 +6938,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C23" s="5">
         <f>1-Assumptions!C22</f>
@@ -6963,10 +6958,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C24" s="5">
         <f>1-Assumptions!C23</f>
@@ -6983,15 +6978,15 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C27" s="14">
         <f>(C17*C22-Assumptions!C26-Assumptions!C31+Assumptions!C36)*(1-Assumptions!C41)</f>
@@ -7008,10 +7003,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C28" s="14">
         <f>(C18*C23-Assumptions!C27-Assumptions!C32+Assumptions!C37)*(1-Assumptions!C42)</f>
@@ -7028,10 +7023,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C29" s="14">
         <f>(C19*C24-Assumptions!C28-Assumptions!C33+Assumptions!C38)*(1-Assumptions!C43)</f>
@@ -7048,15 +7043,15 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C32" s="14">
         <f>C27/Assumptions!$C$8*10</f>
@@ -7073,10 +7068,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C33" s="14">
         <f>C28/Assumptions!$C$8*10</f>
@@ -7093,10 +7088,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C34" s="14">
         <f>C29/Assumptions!$C$8*10</f>
@@ -7113,15 +7108,15 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C37" s="14">
         <f>(C17*C22-(C17*C22-Assumptions!C26-Assumptions!C31+Assumptions!C36)*Assumptions!C41-Assumptions!C31+Assumptions!$C$73*C17)-Assumptions!C69*C17</f>
@@ -7138,10 +7133,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C38" s="14">
         <f>(C18*C23-(C18*C23-Assumptions!C27-Assumptions!C32+Assumptions!C37)*Assumptions!C42-Assumptions!C32+Assumptions!$C$73*C18)-Assumptions!C70*C18</f>
@@ -7158,10 +7153,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C39" s="14">
         <f>(C19*C24-(C19*C24-Assumptions!C28-Assumptions!C33+Assumptions!C38)*Assumptions!C43-Assumptions!C33+Assumptions!$C$73*C19)-Assumptions!C71*C19</f>
@@ -7178,20 +7173,20 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B45" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C45" s="14">
         <f>$C$9/C27</f>
@@ -7204,10 +7199,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B46" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C46" s="14">
         <f t="shared" ref="C46:D46" si="0">$C$9/C28</f>
@@ -7220,10 +7215,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C47" s="14">
         <f t="shared" ref="C47:D47" si="1">$C$9/C29</f>
@@ -7240,17 +7235,17 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C50" s="14">
         <f t="shared" ref="C50:D52" si="2">$C$10/(C22*C17)</f>
@@ -7263,10 +7258,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B51" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C51" s="14">
         <f t="shared" si="2"/>
@@ -7279,10 +7274,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C52" s="14">
         <f t="shared" si="2"/>
@@ -7295,15 +7290,15 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C55" s="14">
         <f>$C$9/C37</f>
@@ -7316,10 +7311,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B56" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C56" s="14">
         <f t="shared" ref="C56:D57" si="3">$C$9/C38</f>
@@ -7332,10 +7327,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B57" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C57" s="14">
         <f t="shared" si="3"/>
@@ -7348,26 +7343,26 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C62" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D62" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E62" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B64" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C64">
         <v>35</v>
@@ -7381,10 +7376,10 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B65" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C65" s="14">
         <f>C64*D32</f>
@@ -7401,10 +7396,10 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B66" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C66" s="5">
         <f>C65/$C$7-1</f>
@@ -7421,10 +7416,10 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B68" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C68" s="5">
         <v>0.25</v>
@@ -7443,10 +7438,10 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B70" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C70" s="14">
         <f>C68*C65+D68*D65+E68*E65</f>
@@ -7455,10 +7450,10 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B71" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C71" s="5">
         <f>C70/C7-1</f>
@@ -7471,10 +7466,10 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D73" s="14"/>
     </row>

--- a/Delhivery_Financial_Model.xlsx
+++ b/Delhivery_Financial_Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akbar\Desktop\Delhivery Research\3. Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F259DD7-C6AA-4267-A5C4-508E23919640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCEE82A0-2FB7-4C39-A775-8A625D80AC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="853" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -325,7 +325,7 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Case declined FY24-FY26. Investments liquidated to fund Ecom Express acquisition.</t>
+Case declined FY24-FY26. Cash used to fund Ecom Express acquisition, along with investments liquidation.</t>
         </r>
       </text>
     </comment>
@@ -1633,9 +1633,6 @@
     <xf numFmtId="10" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1649,6 +1646,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="6" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1994,7 +1994,7 @@
       <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="56">
         <v>457.9</v>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       <c r="B11" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="56">
         <f>'Scenario Summary'!C68</f>
         <v>580.41757073004101</v>
       </c>
@@ -6811,13 +6811,13 @@
       <c r="C72" s="22"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C73" s="51" t="s">
+      <c r="C73" s="50" t="s">
         <v>217</v>
       </c>
-      <c r="D73" s="52"/>
-      <c r="E73" s="52"/>
-      <c r="F73" s="52"/>
-      <c r="G73" s="52"/>
+      <c r="D73" s="51"/>
+      <c r="E73" s="51"/>
+      <c r="F73" s="51"/>
+      <c r="G73" s="51"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B74" s="7">
@@ -6841,7 +6841,7 @@
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="50" t="s">
+      <c r="A75" s="57" t="s">
         <v>134</v>
       </c>
       <c r="B75" s="8">
@@ -6865,7 +6865,7 @@
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="50"/>
+      <c r="A76" s="57"/>
       <c r="B76" s="8">
         <v>0.12</v>
       </c>
@@ -6886,7 +6886,7 @@
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="50"/>
+      <c r="A77" s="57"/>
       <c r="B77" s="8">
         <v>0.13</v>
       </c>
@@ -6907,7 +6907,7 @@
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="50"/>
+      <c r="A78" s="57"/>
       <c r="B78" s="8">
         <v>0.14000000000000001</v>
       </c>
@@ -6928,7 +6928,7 @@
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="50"/>
+      <c r="A79" s="57"/>
       <c r="B79" s="8">
         <v>0.15</v>
       </c>
@@ -7722,15 +7722,15 @@
       <c r="B63" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C63" s="53">
+      <c r="C63" s="52">
         <f>C62*D30</f>
         <v>224.88741253171955</v>
       </c>
-      <c r="D63" s="53">
+      <c r="D63" s="52">
         <f>D62*D31</f>
         <v>522.9467128635564</v>
       </c>
-      <c r="E63" s="53">
+      <c r="E63" s="52">
         <f>E62*D32</f>
         <v>1050.8894446613315</v>
       </c>
@@ -7784,7 +7784,7 @@
       <c r="B68" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C68" s="55">
+      <c r="C68" s="54">
         <f>C66*C63+D66*D63+E66*E63</f>
         <v>580.41757073004101</v>
       </c>
@@ -7806,10 +7806,10 @@
       <c r="D70" s="7"/>
     </row>
     <row r="71" spans="1:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="A71" s="56" t="s">
+      <c r="A71" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="C71" s="54" t="s">
+      <c r="C71" s="53" t="s">
         <v>109</v>
       </c>
       <c r="D71" s="7"/>

--- a/Delhivery_Financial_Model.xlsx
+++ b/Delhivery_Financial_Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akbar\Desktop\Delhivery Research\3. Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCEE82A0-2FB7-4C39-A775-8A625D80AC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC4B387-B9B6-44E1-BC30-6C95455D0648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="853" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -591,7 +591,7 @@
     <author>akbar</author>
   </authors>
   <commentList>
-    <comment ref="C20" authorId="0" shapeId="0" xr:uid="{BFC675CF-4CCB-4454-813D-2D4541B722F3}">
+    <comment ref="C28" authorId="0" shapeId="0" xr:uid="{BFC675CF-4CCB-4454-813D-2D4541B722F3}">
       <text>
         <r>
           <rPr>
@@ -615,7 +615,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C89" authorId="0" shapeId="0" xr:uid="{61FAB439-F487-496D-953F-327149998EB7}">
+    <comment ref="C97" authorId="0" shapeId="0" xr:uid="{61FAB439-F487-496D-953F-327149998EB7}">
       <text>
         <r>
           <rPr>
@@ -644,7 +644,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="226">
   <si>
     <t>DELHIVERY LIMITED</t>
   </si>
@@ -1283,9 +1283,6 @@
     <t>Q1 FY27</t>
   </si>
   <si>
-    <t>Forward PEG Ratio (P/E / Revenue Growth %)</t>
-  </si>
-  <si>
     <t>It reflects that Delhivery is a high-growth company whose value lies primarily in long-term cash flow generation beyond our 5-year explicit projection period.</t>
   </si>
   <si>
@@ -1341,6 +1338,30 @@
   </si>
   <si>
     <t>SCENARIO ANALYSIS</t>
+  </si>
+  <si>
+    <t>Risk-free Rate</t>
+  </si>
+  <si>
+    <t>Equity Risk Premium</t>
+  </si>
+  <si>
+    <t>Beta</t>
+  </si>
+  <si>
+    <t>Cost of Equity</t>
+  </si>
+  <si>
+    <t>Equity Weight</t>
+  </si>
+  <si>
+    <t>Debt Weight</t>
+  </si>
+  <si>
+    <t>Tax Rate</t>
+  </si>
+  <si>
+    <t>After-Tax Cost of Debt</t>
   </si>
 </sst>
 </file>
@@ -1566,7 +1587,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -1649,6 +1670,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2000,7 +2022,7 @@
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C11" s="56">
         <f>'Scenario Summary'!C68</f>
@@ -2042,7 +2064,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="33.6" x14ac:dyDescent="0.65">
       <c r="A1" s="25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2072,7 +2094,7 @@
       <c r="B6" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <f>Cover!C10</f>
         <v>457.9</v>
       </c>
@@ -2724,7 +2746,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="31.2" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2742,22 +2764,22 @@
         <v>25</v>
       </c>
       <c r="C3" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="E3" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="F3" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="G3" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="H3" s="19" t="s">
         <v>207</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>208</v>
       </c>
       <c r="I3" s="20" t="s">
         <v>20</v>
@@ -3575,7 +3597,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="31.2" x14ac:dyDescent="0.6">
       <c r="A1" s="36" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B1" s="36"/>
       <c r="C1" s="36"/>
@@ -3593,22 +3615,22 @@
         <v>29</v>
       </c>
       <c r="C3" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="E3" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="F3" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="G3" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="H3" s="19" t="s">
         <v>207</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>208</v>
       </c>
       <c r="I3" s="20" t="s">
         <v>20</v>
@@ -4329,7 +4351,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="31.2" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4347,22 +4369,22 @@
         <v>29</v>
       </c>
       <c r="C3" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="E3" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="F3" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="G3" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="H3" s="19" t="s">
         <v>207</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>208</v>
       </c>
       <c r="I3" s="20" t="s">
         <v>20</v>
@@ -5382,7 +5404,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.21875" style="3" bestFit="1" customWidth="1"/>
@@ -5397,7 +5419,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="31.2" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -5773,144 +5795,116 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
-        <v>199</v>
+        <v>104</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="7">
-        <f>C17/C10/100</f>
-        <v>5.8844369061846793</v>
-      </c>
-      <c r="D18" s="7">
-        <f t="shared" ref="D18:G18" si="5">D17/D10/100</f>
-        <v>1.1861454532890003</v>
-      </c>
-      <c r="E18" s="7">
-        <f t="shared" si="5"/>
-        <v>9.4684997174705874</v>
-      </c>
-      <c r="F18" s="7">
-        <f t="shared" si="5"/>
-        <v>-4.0980178340411051</v>
-      </c>
-      <c r="G18" s="7">
-        <f t="shared" si="5"/>
-        <v>3.7316523474400789</v>
+        <v>91</v>
+      </c>
+      <c r="C18" s="30">
+        <v>498</v>
+      </c>
+      <c r="D18" s="30">
+        <v>158</v>
+      </c>
+      <c r="E18" s="30">
+        <v>25</v>
+      </c>
+      <c r="F18" s="30">
+        <v>35</v>
+      </c>
+      <c r="G18" s="30">
+        <f>'Cash Flow'!H11</f>
+        <v>506</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" s="30">
-        <v>498</v>
-      </c>
-      <c r="D19" s="30">
-        <v>158</v>
-      </c>
-      <c r="E19" s="30">
-        <v>25</v>
-      </c>
-      <c r="F19" s="30">
-        <v>35</v>
-      </c>
-      <c r="G19" s="30">
-        <f>'Cash Flow'!H11</f>
-        <v>506</v>
+        <v>26</v>
+      </c>
+      <c r="C19" s="8">
+        <f>C18/C11</f>
+        <v>4.3360905528950805E-2</v>
+      </c>
+      <c r="D19" s="8">
+        <f>D18/D11</f>
+        <v>1.0711864406779662E-2</v>
+      </c>
+      <c r="E19" s="8">
+        <f>E18/E11</f>
+        <v>1.2370113805047007E-2</v>
+      </c>
+      <c r="F19" s="8">
+        <f>F18/F11</f>
+        <v>3.629199502281211E-3</v>
+      </c>
+      <c r="G19" s="8">
+        <f>G18/G11</f>
+        <v>1.4667781443065348E-2</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="8">
-        <f>C19/C11</f>
-        <v>4.3360905528950805E-2</v>
+        <f>C18/C5</f>
+        <v>8.1094284318514898E-2</v>
       </c>
       <c r="D20" s="8">
-        <f t="shared" ref="D20:G20" si="6">D19/D11</f>
-        <v>1.0711864406779662E-2</v>
+        <f>D18/D5</f>
+        <v>3.8725490196078433E-2</v>
       </c>
       <c r="E20" s="8">
-        <f t="shared" si="6"/>
-        <v>1.2370113805047007E-2</v>
+        <f>E18/E5</f>
+        <v>2.0226537216828478E-2</v>
       </c>
       <c r="F20" s="8">
-        <f t="shared" si="6"/>
-        <v>3.629199502281211E-3</v>
+        <f>F18/F5</f>
+        <v>1.7292490118577076E-2</v>
       </c>
       <c r="G20" s="8">
-        <f t="shared" si="6"/>
-        <v>1.4667781443065348E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="8">
-        <f>C19/C5</f>
-        <v>8.1094284318514898E-2</v>
-      </c>
-      <c r="D21" s="8">
-        <f t="shared" ref="D21:G21" si="7">D19/D5</f>
-        <v>3.8725490196078433E-2</v>
-      </c>
-      <c r="E21" s="8">
-        <f t="shared" si="7"/>
-        <v>2.0226537216828478E-2</v>
-      </c>
-      <c r="F21" s="8">
-        <f t="shared" si="7"/>
-        <v>1.7292490118577076E-2</v>
-      </c>
-      <c r="G21" s="8">
-        <f t="shared" si="7"/>
+        <f>G18/G5</f>
         <v>4.815378759040731E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5925,7 +5919,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.77734375" style="3" customWidth="1"/>
@@ -5939,7 +5933,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="31.2" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -5961,1123 +5955,1216 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>134</v>
+        <v>218</v>
       </c>
       <c r="B5" s="46" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="47">
-        <v>0.13</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="B6" s="46" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="47">
-        <v>0.04</v>
+        <v>5.5E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="47">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="58">
+        <f>C5+C7*C6</f>
+        <v>0.13600000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="58">
+        <f>'Income Statement'!H21/'Balance Sheet'!H10*(1-C8)</f>
+        <v>7.6773752563226258E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="58">
+        <f>'Balance Sheet'!H8/('Balance Sheet'!H8+'Balance Sheet'!H10)</f>
+        <v>0.86878923766816141</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="58">
+        <f>'Balance Sheet'!H10/('Balance Sheet'!H8+'Balance Sheet'!H10)</f>
+        <v>0.13121076233183857</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="58">
+        <f>C11*C9+C12*C10</f>
+        <v>0.12822887892376683</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="47">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C15" s="7">
         <f>'Balance Sheet'!H27</f>
         <v>1219</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C16" s="7">
         <f>Assumptions!C7</f>
         <v>753.38235294117635</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C10" s="19" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C18" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D18" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E18" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F18" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G18" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H18" s="19" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="7">
+      <c r="B22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="7">
         <f>'Scenario Summary'!C36</f>
         <v>481.37249999999972</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D22" s="7">
         <f>'Scenario Summary'!D36</f>
         <v>833.24349999999981</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E22" s="7">
         <f>'Scenario Summary'!E36</f>
         <v>1104.369432</v>
       </c>
-      <c r="F14" s="3">
-        <f>E14*1.15</f>
+      <c r="F22" s="3">
+        <f>E22*1.15</f>
         <v>1270.0248467999998</v>
       </c>
-      <c r="G14" s="3">
-        <f>F14*1.12</f>
+      <c r="G22" s="3">
+        <f>F22*1.12</f>
         <v>1422.4278284159998</v>
       </c>
-      <c r="H14" s="3">
-        <f>G14*(1+C6)/(C5-C6)</f>
-        <v>16436.943795029332</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="19" t="s">
+      <c r="H22" s="3">
+        <f>G22*(1+C14)/(C13-C14)</f>
+        <v>16766.901717416516</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="8">
-        <f>C14/'Cash Flow'!H11-1</f>
+      <c r="C23" s="8">
+        <f>C22/'Cash Flow'!H11-1</f>
         <v>-4.8670948616601373E-2</v>
       </c>
-      <c r="D15" s="8">
-        <f>D14/C14-1</f>
+      <c r="D23" s="8">
+        <f>D22/C22-1</f>
         <v>0.73097445325605492</v>
       </c>
-      <c r="E15" s="8">
-        <f t="shared" ref="E15:G15" si="0">E14/D14-1</f>
+      <c r="E23" s="8">
+        <f t="shared" ref="E23:G23" si="0">E22/D22-1</f>
         <v>0.32538619503182464</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F23" s="8">
         <f t="shared" si="0"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G23" s="8">
         <f t="shared" si="0"/>
         <v>0.12000000000000011</v>
       </c>
-      <c r="H15" s="8">
-        <f>C6</f>
+      <c r="H23" s="8">
+        <f>C14</f>
         <v>0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C16" s="7">
-        <f>1/(1+$C$5)</f>
-        <v>0.88495575221238942</v>
-      </c>
-      <c r="D16" s="7">
-        <f>1/(1+$C$5)^2</f>
-        <v>0.78314668337379612</v>
-      </c>
-      <c r="E16" s="7">
-        <f>1/(1+$C$5)^3</f>
-        <v>0.69305016227769578</v>
-      </c>
-      <c r="F16" s="7">
-        <f>1/(1+$C$5)^4</f>
-        <v>0.61331872767937679</v>
-      </c>
-      <c r="G16" s="7">
-        <f>1/(1+$C$5)^5</f>
-        <v>0.54275993599944861</v>
-      </c>
-      <c r="H16" s="7">
-        <f>G16</f>
-        <v>0.54275993599944861</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="19" t="s">
+      <c r="C24" s="7">
+        <f>1/(1+$C$13)</f>
+        <v>0.88634497723007566</v>
+      </c>
+      <c r="D24" s="7">
+        <f>1/(1+$C$13)^2</f>
+        <v>0.78560741866098338</v>
+      </c>
+      <c r="E24" s="7">
+        <f>1/(1+$C$13)^3</f>
+        <v>0.69631918960484784</v>
+      </c>
+      <c r="F24" s="7">
+        <f>1/(1+$C$13)^4</f>
+        <v>0.61717901625517368</v>
+      </c>
+      <c r="G24" s="7">
+        <f>1/(1+$C$13)^5</f>
+        <v>0.54703352110957237</v>
+      </c>
+      <c r="H24" s="7">
+        <f>G24</f>
+        <v>0.54703352110957237</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="7">
-        <f>C14*C16</f>
-        <v>425.99336283185818</v>
-      </c>
-      <c r="D17" s="7">
-        <f t="shared" ref="D17:H17" si="1">D14*D16</f>
-        <v>652.55188346777356</v>
-      </c>
-      <c r="E17" s="7">
+      <c r="B25" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="7">
+        <f>C22*C24</f>
+        <v>426.66209755168433</v>
+      </c>
+      <c r="D25" s="7">
+        <f t="shared" ref="D25:H25" si="1">D22*D24</f>
+        <v>654.60227515104293</v>
+      </c>
+      <c r="E25" s="7">
         <f t="shared" si="1"/>
-        <v>765.38341406212669</v>
-      </c>
-      <c r="F17" s="7">
+        <v>768.99362791460612</v>
+      </c>
+      <c r="F25" s="7">
         <f t="shared" si="1"/>
-        <v>778.9300231605713</v>
-      </c>
-      <c r="G17" s="7">
+        <v>783.83268556765154</v>
+      </c>
+      <c r="G25" s="7">
         <f t="shared" si="1"/>
-        <v>772.03683711490271</v>
-      </c>
-      <c r="H17" s="7">
+        <v>778.11570350264697</v>
+      </c>
+      <c r="H25" s="7">
         <f t="shared" si="1"/>
-        <v>8921.3145622166539</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="19" t="s">
+        <v>9172.0572845764927</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" s="7">
-        <f>SUM(C17:G17)</f>
-        <v>3394.895520637232</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="19" t="s">
+      <c r="B27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="7">
+        <f>SUM(C25:G25)</f>
+        <v>3412.2063896876316</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" s="7">
-        <f>H17</f>
-        <v>8921.3145622166539</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="19" t="s">
+      <c r="B28" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="7">
+        <f>H25</f>
+        <v>9172.0572845764927</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="7">
-        <f>C19+C20</f>
-        <v>12316.210082853886</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="49" t="s">
+      <c r="B29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" s="7">
+        <f>C27+C28</f>
+        <v>12584.263674264124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="49" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="11">
+      <c r="B30" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="11">
         <f>'Balance Sheet'!H27</f>
         <v>1219</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="19" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" s="7">
-        <f>C21-C22</f>
-        <v>11097.210082853886</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="19" t="s">
+      <c r="B31" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="7">
+        <f>C29-C30</f>
+        <v>11365.263674264124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B32" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C32" s="7">
         <f>Assumptions!C7</f>
         <v>753.38235294117635</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="19" t="s">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B33" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C25" s="7">
-        <f>C23/C24*10</f>
-        <v>147.29851369003794</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="19" t="s">
+      <c r="C33" s="7">
+        <f>C31/C32*10</f>
+        <v>150.85651568416174</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C34" s="7">
         <f>Assumptions!C6</f>
         <v>457.9</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="19" t="s">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="8">
-        <f>C25/C26-1</f>
-        <v>-0.67831728829430449</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
+      <c r="C35" s="8">
+        <f>C33/C34-1</f>
+        <v>-0.67054702842506719</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="12" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="19" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" s="7">
+      <c r="B39" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" s="7">
         <f>'Scenario Summary'!C35</f>
         <v>260.54479999999967</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D39" s="7">
         <f>'Scenario Summary'!D35</f>
         <v>470.28587999999968</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E39" s="7">
         <f>'Scenario Summary'!E35</f>
         <v>586.87164159999963</v>
       </c>
-      <c r="F31" s="7">
-        <f>E31*1.08</f>
+      <c r="F39" s="7">
+        <f>E39*1.08</f>
         <v>633.82137292799962</v>
       </c>
-      <c r="G31" s="3">
-        <f>F31*1.06</f>
+      <c r="G39" s="3">
+        <f>F39*1.06</f>
         <v>671.85065530367967</v>
       </c>
-      <c r="H31" s="3">
-        <f>G31*(1+C6)/(C5-C6)</f>
-        <v>7763.6075723980766</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="19" t="s">
+      <c r="H39" s="3">
+        <f>G39*(1+C14)/(C13-C14)</f>
+        <v>7919.4555120614432</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B40" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="8">
-        <f>C31/'Cash Flow'!H11-1</f>
+      <c r="C40" s="8">
+        <f>C39/'Cash Flow'!H11-1</f>
         <v>-0.48508932806324179</v>
       </c>
-      <c r="D32" s="8">
-        <f>D31/C31-1</f>
+      <c r="D40" s="8">
+        <f>D39/C39-1</f>
         <v>0.80500965668860136</v>
       </c>
-      <c r="E32" s="8">
-        <f t="shared" ref="E32:G32" si="2">E31/D31-1</f>
+      <c r="E40" s="8">
+        <f t="shared" ref="E40:G40" si="2">E39/D39-1</f>
         <v>0.24790402297428127</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F40" s="8">
         <f t="shared" si="2"/>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G40" s="8">
         <f t="shared" si="2"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="H32" s="8">
-        <f>C6</f>
+      <c r="H40" s="8">
+        <f>C14</f>
         <v>0.04</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="19" t="s">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C33" s="7">
-        <f>1/(1+$C$5)</f>
-        <v>0.88495575221238942</v>
-      </c>
-      <c r="D33" s="7">
-        <f>1/(1+$C$5)^2</f>
-        <v>0.78314668337379612</v>
-      </c>
-      <c r="E33" s="7">
-        <f>1/(1+$C$5)^3</f>
-        <v>0.69305016227769578</v>
-      </c>
-      <c r="F33" s="7">
-        <f>1/(1+$C$5)^4</f>
-        <v>0.61331872767937679</v>
-      </c>
-      <c r="G33" s="7">
-        <f>1/(1+$C$5)^5</f>
-        <v>0.54275993599944861</v>
-      </c>
-      <c r="H33" s="7">
-        <f>G33</f>
-        <v>0.54275993599944861</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="19" t="s">
+      <c r="C41" s="7">
+        <f>1/(1+$C$13)</f>
+        <v>0.88634497723007566</v>
+      </c>
+      <c r="D41" s="7">
+        <f>1/(1+$C$13)^2</f>
+        <v>0.78560741866098338</v>
+      </c>
+      <c r="E41" s="7">
+        <f>1/(1+$C$13)^3</f>
+        <v>0.69631918960484784</v>
+      </c>
+      <c r="F41" s="7">
+        <f>1/(1+$C$13)^4</f>
+        <v>0.61717901625517368</v>
+      </c>
+      <c r="G41" s="7">
+        <f>1/(1+$C$13)^5</f>
+        <v>0.54703352110957237</v>
+      </c>
+      <c r="H41" s="7">
+        <f>G41</f>
+        <v>0.54703352110957237</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C34" s="7">
-        <f>C31*C33</f>
-        <v>230.57061946902627</v>
-      </c>
-      <c r="D34" s="7">
-        <f t="shared" ref="D34:H34" si="3">D31*D33</f>
-        <v>368.30282715952683</v>
-      </c>
-      <c r="E34" s="7">
+      <c r="B42" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" s="7">
+        <f>C39*C41</f>
+        <v>230.93257482341431</v>
+      </c>
+      <c r="D42" s="7">
+        <f t="shared" ref="D42:H42" si="3">D39*D41</f>
+        <v>369.46007621950872</v>
+      </c>
+      <c r="E42" s="7">
         <f t="shared" si="3"/>
-        <v>406.73148644705748</v>
-      </c>
-      <c r="F34" s="7">
+        <v>408.64998588097848</v>
+      </c>
+      <c r="F42" s="7">
         <f t="shared" si="3"/>
-        <v>388.7345180201965</v>
-      </c>
-      <c r="G34" s="7">
+        <v>391.18125142520637</v>
+      </c>
+      <c r="G42" s="7">
         <f t="shared" si="3"/>
-        <v>364.65361867381279</v>
-      </c>
-      <c r="H34" s="7">
+        <v>367.52482963054547</v>
+      </c>
+      <c r="H42" s="7">
         <f t="shared" si="3"/>
-        <v>4213.775149119615</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="19" t="s">
+        <v>4332.2076340335825</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C36" s="3">
-        <f>SUM(C34:G34)</f>
-        <v>1758.99306976962</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="19" t="s">
+      <c r="B44" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="3">
+        <f>SUM(C42:G42)</f>
+        <v>1767.7487179796531</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="3">
-        <f>H34</f>
-        <v>4213.775149119615</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="19" t="s">
+      <c r="B45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="3">
+        <f>H42</f>
+        <v>4332.2076340335825</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" s="3">
-        <f>C36+C37</f>
-        <v>5972.768218889235</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="49" t="s">
+      <c r="B46" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="3">
+        <f>C44+C45</f>
+        <v>6099.956352013236</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="49" t="s">
         <v>146</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" s="11">
+      <c r="B47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" s="11">
         <f>'Balance Sheet'!H27</f>
         <v>1219</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="19" t="s">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C40" s="11">
-        <f>C38-C39</f>
-        <v>4753.768218889235</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="19" t="s">
+      <c r="B48" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" s="11">
+        <f>C46-C47</f>
+        <v>4880.956352013236</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B49" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C49" s="7">
         <f>Assumptions!C7</f>
         <v>753.38235294117635</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="19" t="s">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B50" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="7">
-        <f>C40/C41*10</f>
-        <v>63.099012079732191</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="19" t="s">
+      <c r="C50" s="7">
+        <f>C48/C49*10</f>
+        <v>64.787240276576242</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B51" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C51" s="7">
         <f>Assumptions!C6</f>
         <v>457.9</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="19" t="s">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B52" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="8">
-        <f>C42/C43-1</f>
-        <v>-0.86219914374376017</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="12" t="s">
+      <c r="C52" s="8">
+        <f>C50/C51-1</f>
+        <v>-0.85851225097930506</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="12" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="19" t="s">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C48" s="7">
+      <c r="B56" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C56" s="7">
         <f>'Scenario Summary'!C37</f>
         <v>805.6618999999996</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D56" s="7">
         <f>'Scenario Summary'!D37</f>
         <v>1369.9175</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E56" s="7">
         <f>'Scenario Summary'!E37</f>
         <v>1823.9074229999999</v>
       </c>
-      <c r="F48" s="3">
-        <f>E48*1.2</f>
+      <c r="F56" s="3">
+        <f>E56*1.2</f>
         <v>2188.6889075999998</v>
       </c>
-      <c r="G48" s="3">
-        <f>F48*1.15</f>
+      <c r="G56" s="3">
+        <f>F56*1.15</f>
         <v>2516.9922437399996</v>
       </c>
-      <c r="H48" s="3">
-        <f>G48*(1+C6)/(C5-C6)</f>
-        <v>29085.24370544</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="19" t="s">
+      <c r="H56" s="3">
+        <f>G56*(1+C14)/(C13-C14)</f>
+        <v>29669.105687621508</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B57" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="8">
-        <f>C48/'Cash Flow'!H11-1</f>
+      <c r="C57" s="8">
+        <f>C56/'Cash Flow'!H11-1</f>
         <v>0.59221719367588865</v>
       </c>
-      <c r="D49" s="8">
-        <f>D48/C48-1</f>
+      <c r="D57" s="8">
+        <f>D56/C56-1</f>
         <v>0.70036277004038627</v>
       </c>
-      <c r="E49" s="8">
-        <f t="shared" ref="E49:G49" si="4">E48/D48-1</f>
+      <c r="E57" s="8">
+        <f t="shared" ref="E57:G57" si="4">E56/D56-1</f>
         <v>0.33139946237638385</v>
       </c>
-      <c r="F49" s="8">
+      <c r="F57" s="8">
         <f t="shared" si="4"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="G49" s="8">
+      <c r="G57" s="8">
         <f t="shared" si="4"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="H49" s="8">
+      <c r="H57" s="8">
         <v>0.04</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="19" t="s">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C50" s="7">
-        <f>1/(1+$C$5)</f>
-        <v>0.88495575221238942</v>
-      </c>
-      <c r="D50" s="7">
-        <f>1/(1+$C$5)^2</f>
-        <v>0.78314668337379612</v>
-      </c>
-      <c r="E50" s="7">
-        <f>1/(1+$C$5)^3</f>
-        <v>0.69305016227769578</v>
-      </c>
-      <c r="F50" s="7">
-        <f>1/(1+$C$5)^4</f>
-        <v>0.61331872767937679</v>
-      </c>
-      <c r="G50" s="7">
-        <f>1/(1+$C$5)^5</f>
-        <v>0.54275993599944861</v>
-      </c>
-      <c r="H50" s="7">
-        <f>G50</f>
-        <v>0.54275993599944861</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="19" t="s">
+      <c r="C58" s="7">
+        <f>1/(1+$C$13)</f>
+        <v>0.88634497723007566</v>
+      </c>
+      <c r="D58" s="7">
+        <f>1/(1+$C$13)^2</f>
+        <v>0.78560741866098338</v>
+      </c>
+      <c r="E58" s="7">
+        <f>1/(1+$C$13)^3</f>
+        <v>0.69631918960484784</v>
+      </c>
+      <c r="F58" s="7">
+        <f>1/(1+$C$13)^4</f>
+        <v>0.61717901625517368</v>
+      </c>
+      <c r="G58" s="7">
+        <f>1/(1+$C$13)^5</f>
+        <v>0.54703352110957237</v>
+      </c>
+      <c r="H58" s="7">
+        <f>G58</f>
+        <v>0.54703352110957237</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C51" s="3">
-        <f>C48*C50</f>
-        <v>712.97513274336256</v>
-      </c>
-      <c r="D51" s="3">
-        <f t="shared" ref="D51:H51" si="5">D48*D50</f>
-        <v>1072.8463466207224</v>
-      </c>
-      <c r="E51" s="3">
+      <c r="B59" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C59" s="3">
+        <f>C56*C58</f>
+        <v>714.09437841063914</v>
+      </c>
+      <c r="D59" s="3">
+        <f t="shared" ref="D59:H59" si="5">D56*D58</f>
+        <v>1076.2173509535078</v>
+      </c>
+      <c r="E59" s="3">
         <f t="shared" si="5"/>
-        <v>1264.0593354896439</v>
-      </c>
-      <c r="F51" s="3">
+        <v>1270.0217386976262</v>
+      </c>
+      <c r="F59" s="3">
         <f t="shared" si="5"/>
-        <v>1342.3638960951969</v>
-      </c>
-      <c r="G51" s="3">
+        <v>1350.8128668811785</v>
+      </c>
+      <c r="G59" s="3">
         <f t="shared" si="5"/>
-        <v>1366.1225491234306</v>
-      </c>
-      <c r="H51" s="3">
+        <v>1376.8791296985751</v>
+      </c>
+      <c r="H59" s="3">
         <f t="shared" si="5"/>
-        <v>15786.30501209298</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="19" t="s">
+        <v>16229.995352471635</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C53" s="3">
-        <f>SUM(C51:G51)</f>
-        <v>5758.3672600723567</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="19" t="s">
+      <c r="B61" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C61" s="3">
+        <f>SUM(C59:G59)</f>
+        <v>5788.0254646415269</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C54" s="3">
-        <f>H51</f>
-        <v>15786.30501209298</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="19" t="s">
+      <c r="B62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C62" s="3">
+        <f>H59</f>
+        <v>16229.995352471635</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C55" s="3">
-        <f>C53+C54</f>
-        <v>21544.672272165335</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="49" t="s">
+      <c r="B63" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C63" s="3">
+        <f>C61+C62</f>
+        <v>22018.02081711316</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="49" t="s">
         <v>146</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C56" s="11">
+      <c r="B64" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C64" s="11">
         <f>'Balance Sheet'!H27</f>
         <v>1219</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="19" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C57" s="11">
-        <f>C55-C56</f>
-        <v>20325.672272165335</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="19" t="s">
+      <c r="B65" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C65" s="11">
+        <f>C63-C64</f>
+        <v>20799.02081711316</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B66" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C58" s="7">
+      <c r="C66" s="7">
         <f>Assumptions!C7</f>
         <v>753.38235294117635</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="19" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B67" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C59" s="7">
-        <f>C57/C58*10</f>
-        <v>269.79225346618057</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="19" t="s">
+      <c r="C67" s="7">
+        <f>C65/C66*10</f>
+        <v>276.07523239580229</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B68" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C68" s="7">
         <f>Assumptions!C6</f>
         <v>457.9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="19" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="19" t="s">
         <v>8</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C61" s="8">
-        <f>C59/C60-1</f>
-        <v>-0.41080529926582099</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="12" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C65" s="7">
-        <f>C42</f>
-        <v>63.099012079732191</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C66" s="7">
-        <f>C25</f>
-        <v>147.29851369003794</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C67" s="7">
-        <f>C59</f>
-        <v>269.79225346618057</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C68" s="7">
-        <f>25%*C65+50%*C66+25%*C67</f>
-        <v>156.87207323149715</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="19" t="s">
-        <v>156</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C69" s="8">
-        <f>C68/Assumptions!C6-1</f>
-        <v>-0.65740975489954756</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+        <f>C67/C68-1</f>
+        <v>-0.39708400874469907</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C73" s="7">
+        <f>C50</f>
+        <v>64.787240276576242</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C74" s="7">
+        <f>C33</f>
+        <v>150.85651568416174</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C75" s="7">
+        <f>C67</f>
+        <v>276.07523239580229</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C76" s="7">
+        <f>25%*C73+50%*C74+25%*C75</f>
+        <v>160.64387601017552</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" s="8">
+        <f>C76/Assumptions!C6-1</f>
+        <v>-0.64917257914353454</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B72" s="22"/>
-      <c r="C72" s="22"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C73" s="50" t="s">
-        <v>217</v>
-      </c>
-      <c r="D73" s="51"/>
-      <c r="E73" s="51"/>
-      <c r="F73" s="51"/>
-      <c r="G73" s="51"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B74" s="7">
-        <f>C25</f>
+      <c r="B80" s="22"/>
+      <c r="C80" s="22"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C81" s="50" t="s">
+        <v>216</v>
+      </c>
+      <c r="D81" s="51"/>
+      <c r="E81" s="51"/>
+      <c r="F81" s="51"/>
+      <c r="G81" s="51"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B82" s="7">
+        <f>C33</f>
+        <v>150.85651568416174</v>
+      </c>
+      <c r="C82" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="D82" s="8">
+        <v>0.04</v>
+      </c>
+      <c r="E82" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="F82" s="8">
+        <v>0.06</v>
+      </c>
+      <c r="G82" s="8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="57" t="s">
+        <v>134</v>
+      </c>
+      <c r="B83" s="8">
+        <v>0.11</v>
+      </c>
+      <c r="C83" s="7">
+        <f t="dataTable" ref="C83:G87" dt2D="1" dtr="1" r1="C14" r2="C13"/>
+        <v>175.84064668385548</v>
+      </c>
+      <c r="D83" s="7">
+        <v>198.04994588644087</v>
+      </c>
+      <c r="E83" s="7">
+        <v>227.66234482322145</v>
+      </c>
+      <c r="F83" s="7">
+        <v>269.11970333471413</v>
+      </c>
+      <c r="G83" s="7">
+        <v>331.30574110195323</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="57"/>
+      <c r="B84" s="8">
+        <v>0.12</v>
+      </c>
+      <c r="C84" s="7">
+        <v>152.8102193213424</v>
+      </c>
+      <c r="D84" s="7">
+        <v>169.47540704027486</v>
+      </c>
+      <c r="E84" s="7">
+        <v>190.90207696461661</v>
+      </c>
+      <c r="F84" s="7">
+        <v>219.47097019707223</v>
+      </c>
+      <c r="G84" s="7">
+        <v>259.46742072251021</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="57"/>
+      <c r="B85" s="8">
+        <v>0.13</v>
+      </c>
+      <c r="C85" s="7">
+        <v>134.4320702944778</v>
+      </c>
+      <c r="D85" s="7">
         <v>147.29851369003794</v>
       </c>
-      <c r="C74" s="8">
-        <v>0.03</v>
-      </c>
-      <c r="D74" s="8">
-        <v>0.04</v>
-      </c>
-      <c r="E74" s="8">
-        <v>0.05</v>
-      </c>
-      <c r="F74" s="8">
-        <v>0.06</v>
-      </c>
-      <c r="G74" s="8">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="57" t="s">
-        <v>134</v>
-      </c>
-      <c r="B75" s="8">
-        <v>0.11</v>
-      </c>
-      <c r="C75" s="7">
-        <f t="dataTable" ref="C75:G79" dt2D="1" dtr="1" r1="C6" r2="C5"/>
-        <v>175.84064668385548</v>
-      </c>
-      <c r="D75" s="7">
-        <v>198.04994588644087</v>
-      </c>
-      <c r="E75" s="7">
-        <v>227.66234482322145</v>
-      </c>
-      <c r="F75" s="7">
-        <v>269.11970333471413</v>
-      </c>
-      <c r="G75" s="7">
-        <v>331.30574110195323</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="57"/>
-      <c r="B76" s="8">
-        <v>0.12</v>
-      </c>
-      <c r="C76" s="7">
-        <v>152.8102193213424</v>
-      </c>
-      <c r="D76" s="7">
-        <v>169.47540704027486</v>
-      </c>
-      <c r="E76" s="7">
-        <v>190.90207696461661</v>
-      </c>
-      <c r="F76" s="7">
-        <v>219.47097019707223</v>
-      </c>
-      <c r="G76" s="7">
-        <v>259.46742072251021</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="57"/>
-      <c r="B77" s="8">
-        <v>0.13</v>
-      </c>
-      <c r="C77" s="7">
-        <v>134.4320702944778</v>
-      </c>
-      <c r="D77" s="7">
-        <v>147.29851369003794</v>
-      </c>
-      <c r="E77" s="7">
+      <c r="E85" s="7">
         <v>163.38156793448809</v>
       </c>
-      <c r="F77" s="7">
+      <c r="F85" s="7">
         <v>184.05978053449547</v>
       </c>
-      <c r="G77" s="7">
+      <c r="G85" s="7">
         <v>211.63073066783863</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="57"/>
-      <c r="B78" s="8">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="57"/>
+      <c r="B86" s="8">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C78" s="7">
+      <c r="C86" s="7">
         <v>119.43564861694898</v>
       </c>
-      <c r="D78" s="7">
+      <c r="D86" s="7">
         <v>129.59819887989121</v>
       </c>
-      <c r="E78" s="7">
+      <c r="E86" s="7">
         <v>142.01909364570949</v>
       </c>
-      <c r="F78" s="7">
+      <c r="F86" s="7">
         <v>157.5452121029823</v>
       </c>
-      <c r="G78" s="7">
+      <c r="G86" s="7">
         <v>177.5073644051902</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="57"/>
-      <c r="B79" s="8">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="57"/>
+      <c r="B87" s="8">
         <v>0.15</v>
       </c>
-      <c r="C79" s="7">
+      <c r="C87" s="7">
         <v>106.97400329672584</v>
       </c>
-      <c r="D79" s="7">
+      <c r="D87" s="7">
         <v>115.15204845718337</v>
       </c>
-      <c r="E79" s="7">
+      <c r="E87" s="7">
         <v>124.96570264973241</v>
       </c>
-      <c r="F79" s="7">
+      <c r="F87" s="7">
         <v>136.96016888507009</v>
       </c>
-      <c r="G79" s="7">
+      <c r="G87" s="7">
         <v>151.95325167924221</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="12" t="s">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="12" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="19" t="s">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B92" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C84" s="7">
+      <c r="C92" s="7">
         <f>Assumptions!C6</f>
         <v>457.9</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="19" t="s">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C85" s="3">
-        <f>C84*C8/10</f>
+      <c r="B93" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C93" s="3">
+        <f>C92*C16/10</f>
         <v>34497.377941176463</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="19" t="s">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C86" s="11">
-        <f>C85+'Balance Sheet'!H27</f>
+      <c r="B94" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C94" s="11">
+        <f>C93+'Balance Sheet'!H27</f>
         <v>35716.377941176463</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="19" t="s">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C87" s="7">
-        <f>C86-C19</f>
-        <v>32321.482420539229</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="19" t="s">
+      <c r="B95" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C95" s="7">
+        <f>C94-C27</f>
+        <v>32304.171551488831</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C88" s="3">
-        <f>C87/H16</f>
-        <v>59550.236258727957</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="19" t="s">
+      <c r="B96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C96" s="3">
+        <f>C95/H24</f>
+        <v>59053.367490103432</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B97" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C89" s="48">
-        <f>(C88/G14*C5-1)/(1+C88/G14)</f>
-        <v>0.10363829397690716</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
+      <c r="C97" s="48">
+        <f>(C96/G22*C13-1)/(1+C96/G22)</f>
+        <v>0.10169224313830395</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="3" t="s">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="3" t="s">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="3" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="3" t="s">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" s="3" t="s">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="3" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" s="3" t="s">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" s="3" t="s">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" s="3" t="s">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="3" t="s">
         <v>165</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A75:A79"/>
+    <mergeCell ref="A83:A87"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -7103,7 +7190,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="31.2" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -7395,15 +7482,15 @@
         <v>90</v>
       </c>
       <c r="C30" s="7">
-        <f>C25/Assumptions!$C$7*10</f>
+        <f>C25/$C$6*10</f>
         <v>3.9349581104821354</v>
       </c>
       <c r="D30" s="7">
-        <f>D25/Assumptions!$C$7*10</f>
+        <f t="shared" ref="D30:E30" si="0">D25/$C$6*10</f>
         <v>6.4253546437634155</v>
       </c>
       <c r="E30" s="7">
-        <f>E25/Assumptions!$C$7*10</f>
+        <f t="shared" si="0"/>
         <v>8.1423859957056379</v>
       </c>
     </row>
@@ -7415,15 +7502,15 @@
         <v>90</v>
       </c>
       <c r="C31" s="7">
-        <f>C26/Assumptions!$C$7*10</f>
+        <f t="shared" ref="C31:E32" si="1">C26/$C$6*10</f>
         <v>6.9544368534062055</v>
       </c>
       <c r="D31" s="7">
-        <f>D26/Assumptions!$C$7*10</f>
+        <f>D26/$C$6*10</f>
         <v>11.621038063634588</v>
       </c>
       <c r="E31" s="7">
-        <f>E26/Assumptions!$C$7*10</f>
+        <f t="shared" si="1"/>
         <v>15.570376017177434</v>
       </c>
     </row>
@@ -7435,15 +7522,15 @@
         <v>90</v>
       </c>
       <c r="C32" s="7">
-        <f>C27/Assumptions!$C$7*10</f>
+        <f t="shared" si="1"/>
         <v>11.277472808901031</v>
       </c>
       <c r="D32" s="7">
-        <f>D27/Assumptions!$C$7*10</f>
+        <f t="shared" si="1"/>
         <v>19.107080812024208</v>
       </c>
       <c r="E32" s="7">
-        <f>E27/Assumptions!$C$7*10</f>
+        <f t="shared" si="1"/>
         <v>26.084049093109517</v>
       </c>
     </row>
@@ -7546,11 +7633,11 @@
         <v>53</v>
       </c>
       <c r="C44" s="7">
-        <f t="shared" ref="C44:D44" si="0">$C$7/C26</f>
+        <f t="shared" ref="C44:D44" si="2">$C$7/C26</f>
         <v>65.842858257563407</v>
       </c>
       <c r="D44" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>39.40267620608649</v>
       </c>
     </row>
@@ -7562,11 +7649,11 @@
         <v>53</v>
       </c>
       <c r="C45" s="7">
-        <f t="shared" ref="C45:D45" si="1">$C$7/C27</f>
+        <f t="shared" ref="C45:D45" si="3">$C$7/C27</f>
         <v>40.603068414280798</v>
       </c>
       <c r="D45" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>23.96493763253676</v>
       </c>
     </row>
@@ -7589,11 +7676,11 @@
         <v>53</v>
       </c>
       <c r="C48" s="7">
-        <f t="shared" ref="C48:D50" si="2">$C$8/(C20*C15)</f>
+        <f t="shared" ref="C48:D50" si="4">$C$8/(C20*C15)</f>
         <v>35.40593867090994</v>
       </c>
       <c r="D48" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>27.366909117611549</v>
       </c>
     </row>
@@ -7605,11 +7692,11 @@
         <v>53</v>
       </c>
       <c r="C49" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>30.213067665843145</v>
       </c>
       <c r="D49" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>21.580762618459385</v>
       </c>
     </row>
@@ -7621,11 +7708,11 @@
         <v>53</v>
       </c>
       <c r="C50" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>24.900879944376218</v>
       </c>
       <c r="D50" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>16.733391322620815</v>
       </c>
     </row>
@@ -7658,11 +7745,11 @@
         <v>53</v>
       </c>
       <c r="C54" s="7">
-        <f t="shared" ref="C54:D55" si="3">$C$7/C36</f>
+        <f t="shared" ref="C54:D55" si="5">$C$7/C36</f>
         <v>71.66462135077613</v>
       </c>
       <c r="D54" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>41.401316591340311</v>
       </c>
     </row>
@@ -7674,11 +7761,11 @@
         <v>53</v>
       </c>
       <c r="C55" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>42.818678581147353</v>
       </c>
       <c r="D55" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>25.182084279656593</v>
       </c>
     </row>
@@ -7747,11 +7834,11 @@
         <v>-0.50887221547997474</v>
       </c>
       <c r="D64" s="8">
-        <f t="shared" ref="D64:E64" si="4">D63/$C$5-1</f>
+        <f t="shared" ref="D64:E64" si="6">D63/$C$5-1</f>
         <v>0.14205440677780401</v>
       </c>
       <c r="E64" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.2950195340933206</v>
       </c>
     </row>
